--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.5</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -653,7 +653,7 @@
     <t>Diagnosekode.</t>
   </si>
   <si>
-    <t>Diagnosekode. Det er mulig å bruke ICD-10, ICD-11, ICPC-2 og SNOMED CT.</t>
+    <t>Diagnosekode. Det er mulig å bruke ICD-10, ICD-11, ICPC-2 og SNOMED CT. Flere koder tillatt for å støtte multippel koding jf. Helsedirektoratets kodeveiledning (spesialisthelsetjenesten).</t>
   </si>
   <si>
     <t>0..1 to account for primarily narrative only resources.</t>
@@ -934,7 +934,7 @@
     <t>ICD-10</t>
   </si>
   <si>
-    <t>ICD-10: Den internasjonale statistiske klassifikasjonen av sykdommer og beslektede helseproblemer.</t>
+    <t>ICD-10: Den internasjonale statistiske klassifikasjonen av sykdommer og beslektede helseproblemer. Flere koder tillatt for å støtte multippel koding jf. Helsedirektoratets kodeveiledning (spesialisthelsetjenesten).</t>
   </si>
   <si>
     <t>Condition.code.coding:ICD10.id</t>
@@ -5078,7 +5078,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.7</t>
+    <t>1.1.8</t>
   </si>
   <si>
     <t>Name</t>
